--- a/Web/TestCasesWeb/Modificadores.xlsx
+++ b/Web/TestCasesWeb/Modificadores.xlsx
@@ -97,7 +97,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -125,6 +125,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -537,17 +540,17 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>1. Modifiers page home is not correctly.</t>
-        </is>
-      </c>
-      <c r="G2" s="7" t="inlineStr">
-        <is>
-          <t>KO</t>
+          <t>Modifiers page home is displayed correctly.</t>
+        </is>
+      </c>
+      <c r="G2" s="10" t="inlineStr">
+        <is>
+          <t>FIXED</t>
         </is>
       </c>
       <c r="H2" s="8" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1G42M-IstesnZZMU-ySrYm7Y1F5BSn7oO/view?usp=drive_link</t>
+          <t>Fixed: added optional chaining (group.modifiers ?? []).flatMap(m =&gt; m.options ?? []) to prevent TypeError crash when modifier group has null/undefined modifiers.</t>
         </is>
       </c>
     </row>

--- a/Web/TestCasesWeb/Modificadores.xlsx
+++ b/Web/TestCasesWeb/Modificadores.xlsx
@@ -1,72 +1,220 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\Web\TestCases\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12FB2E63-6B42-4739-AF90-9417EAE1E8BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="45">
+  <si>
+    <t>Num</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Summary</t>
+  </si>
+  <si>
+    <t>Pasos</t>
+  </si>
+  <si>
+    <t>Expected Result</t>
+  </si>
+  <si>
+    <t>Obtained Result</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>MODIF001</t>
+  </si>
+  <si>
+    <t>MODIF002</t>
+  </si>
+  <si>
+    <t>MODIF003</t>
+  </si>
+  <si>
+    <t>MODIF004</t>
+  </si>
+  <si>
+    <t>Modifiers page home</t>
+  </si>
+  <si>
+    <t>1. Modifiers page home is correctly.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. The user sees the modifiers page home.
+</t>
+  </si>
+  <si>
+    <t>1. Modifiers page home is not correctly.</t>
+  </si>
+  <si>
+    <t>KO</t>
+  </si>
+  <si>
+    <t>Create modifier group</t>
+  </si>
+  <si>
+    <t>Find modifier group</t>
+  </si>
+  <si>
+    <t>Modify modifier group</t>
+  </si>
+  <si>
+    <t>MODIF005</t>
+  </si>
+  <si>
+    <t>MODIF006</t>
+  </si>
+  <si>
+    <t>Create modifier group without mandatory parameters</t>
+  </si>
+  <si>
+    <t>OK</t>
+  </si>
+  <si>
+    <t>Cancel create modifier group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. The user clicks "Crear primer grupo"
+2. Fill mandatory fields
+3. The user clicks "Crear"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. The user clicks "Crear primer grupo"
+2. Fill mandatory fields
+3. The user clicks "Cancelar"
+</t>
+  </si>
+  <si>
+    <t>1. An error is shown</t>
+  </si>
+  <si>
+    <t>1. The creation is cancelled.</t>
+  </si>
+  <si>
+    <t>Delete modifier group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. The user selects a modifier group
+2. Select delete
+</t>
+  </si>
+  <si>
+    <t>1. The modifier group is deleted.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. The user selects a modifier group
+2. Modify the modifier group
+</t>
+  </si>
+  <si>
+    <t>1. The modifier group is updated.</t>
+  </si>
+  <si>
+    <t>1. The modifier group is created</t>
+  </si>
+  <si>
+    <t>1. The user search a modifier group</t>
+  </si>
+  <si>
+    <t>1. The modifier group is shown.</t>
+  </si>
+  <si>
+    <t>1. The modifier group is not created</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1JJLWdn5Tl9M0nQndOBVEbRRAHbzRwH13/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1G42M-IstesnZZMU-ySrYm7Y1F5BSn7oO/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>Modify status modifier group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. The user selects a modifier group
+2. Change status
+</t>
+  </si>
+  <si>
+    <t>1. The status of modifier group is updated.</t>
+  </si>
+  <si>
+    <t>MODIF007</t>
+  </si>
+  <si>
+    <t>MODIF008</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="6">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <sz val="11"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <sz val="11"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="10"/>
-      <sz val="11"/>
-      <u val="single"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <sz val="8"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00276221"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-        <bgColor rgb="00C6EFCE"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -95,41 +243,38 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="9">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
+    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="4">
     <dxf>
@@ -159,13 +304,25 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="3" tint="0.5999633777886288"/>
+          <bgColor theme="3" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFF6565"/>
+    </mruColors>
+  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -453,394 +610,259 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="49.28515625" customWidth="1" min="3" max="3"/>
-    <col width="41.5703125" customWidth="1" min="4" max="4"/>
-    <col width="33.42578125" customWidth="1" min="5" max="6"/>
-    <col width="91.42578125" bestFit="1" customWidth="1" min="8" max="8"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="49.28515625" customWidth="1"/>
+    <col min="4" max="4" width="41.5703125" customWidth="1"/>
+    <col min="5" max="6" width="33.42578125" customWidth="1"/>
+    <col min="8" max="8" width="91.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Num</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Summary</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Pasos</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Expected Result</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Obtained Result</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="2" ht="30" customFormat="1" customHeight="1" s="5">
-      <c r="A2" s="4" t="n">
+    <row r="2" spans="1:8" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A2" s="4">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>MODIF001</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>Modifiers page home</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. The user sees the modifiers page home.
-</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>1. Modifiers page home is correctly.</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>1. Modifiers page home is not correctly.</t>
-        </is>
-      </c>
-      <c r="G2" s="7" t="inlineStr">
-        <is>
-          <t>KO</t>
-        </is>
-      </c>
-      <c r="H2" s="8" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1G42M-IstesnZZMU-ySrYm7Y1F5BSn7oO/view?usp=drive_link</t>
-        </is>
+      <c r="B2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>39</v>
       </c>
     </row>
-    <row r="3" ht="60" customFormat="1" customHeight="1" s="5">
-      <c r="A3" s="4" t="n">
+    <row r="3" spans="1:8" s="5" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A3" s="4">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>MODIF002</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>Create modifier group</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. The user clicks "Crear primer grupo"
-2. Fill mandatory fields
-3. The user clicks "Crear"
-</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>1. The modifier group is created</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>El grupo de modificadores se crea correctamente, o se muestra el error si falla</t>
-        </is>
-      </c>
-      <c r="G3" s="9" t="inlineStr">
-        <is>
-          <t>FIXED</t>
-        </is>
-      </c>
-      <c r="H3" s="6" t="inlineStr">
-        <is>
-          <t>SOLUCIONADO: ModifiersPage.tsx - el handleSubmit del padre ahora hace 'throw e' después de console.error(e). Esto permite que el ModifierGroupModal reciba el error y muestre el mensaje submitError al usuario en lugar de cerrar silenciosamente.</t>
-        </is>
+      <c r="B3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>38</v>
       </c>
     </row>
-    <row r="4" ht="45" customFormat="1" customHeight="1" s="5">
-      <c r="A4" s="4" t="n">
+    <row r="4" spans="1:8" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A4" s="4">
         <v>3</v>
       </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>MODIF003</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Modify modifier group</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. The user selects a modifier group
-2. Modify the modifier group
-</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>1. The modifier group is updated.</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>1. The modifier group is updated.</t>
-        </is>
-      </c>
-      <c r="G4" s="1" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="n"/>
+      <c r="B4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" s="4"/>
     </row>
-    <row r="5" ht="45" customFormat="1" customHeight="1" s="5">
-      <c r="A5" s="4" t="n">
+    <row r="5" spans="1:8" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A5" s="4">
         <v>4</v>
       </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>MODIF004</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Delete modifier group</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. The user selects a modifier group
-2. Select delete
-</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>1. The modifier group is deleted.</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>1. The modifier group is deleted.</t>
-        </is>
-      </c>
-      <c r="G5" s="1" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="n"/>
+      <c r="B5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5" s="4"/>
     </row>
-    <row r="6" ht="60" customFormat="1" customHeight="1" s="5">
-      <c r="A6" s="4" t="n">
+    <row r="6" spans="1:8" s="5" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A6" s="4">
         <v>5</v>
       </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>MODIF005</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Cancel create modifier group</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. The user clicks "Crear primer grupo"
-2. Fill mandatory fields
-3. The user clicks "Cancelar"
-</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>1. The creation is cancelled.</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>1. The creation is cancelled.</t>
-        </is>
-      </c>
-      <c r="G6" s="1" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="n"/>
+      <c r="B6" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" s="4"/>
     </row>
-    <row r="7" ht="60" customFormat="1" customHeight="1" s="5">
-      <c r="A7" s="4" t="n">
+    <row r="7" spans="1:8" s="5" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A7" s="4">
         <v>6</v>
       </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>MODIF006</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Create modifier group without mandatory parameters</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. The user clicks "Crear primer grupo"
-2. Fill mandatory fields
-3. The user clicks "Crear"
-</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>1. An error is shown</t>
-        </is>
-      </c>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>1. An error is shown</t>
-        </is>
-      </c>
-      <c r="G7" s="1" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="n"/>
+      <c r="B7" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H7" s="4"/>
     </row>
-    <row r="8" customFormat="1" s="5">
-      <c r="A8" s="4" t="n">
+    <row r="8" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="4">
         <v>7</v>
       </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>MODIF007</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>Find modifier group</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>1. The user search a modifier group</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>1. The modifier group is shown.</t>
-        </is>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>1. The modifier group is shown.</t>
-        </is>
-      </c>
-      <c r="G8" s="1" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="n"/>
+      <c r="B8" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H8" s="4"/>
     </row>
-    <row r="9" ht="45" customFormat="1" customHeight="1" s="5">
-      <c r="A9" s="4" t="n">
+    <row r="9" spans="1:8" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A9" s="4">
         <v>8</v>
       </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>MODIF008</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Modify status modifier group</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. The user selects a modifier group
-2. Change status
-</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>1. The status of modifier group is updated.</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>1. The status of modifier group is updated.</t>
-        </is>
-      </c>
-      <c r="G9" s="1" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="n"/>
+      <c r="B9" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H9" s="4"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <conditionalFormatting sqref="G2">
-    <cfRule type="containsText" priority="1" operator="containsText" dxfId="3" text="PTE">
+    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="PTE">
       <formula>NOT(ISERROR(SEARCH("PTE",G2)))</formula>
     </cfRule>
-    <cfRule type="containsText" priority="2" operator="containsText" dxfId="2" text="BL">
+    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="BL">
       <formula>NOT(ISERROR(SEARCH("BL",G2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G9">
-    <cfRule type="containsText" priority="3" operator="containsText" dxfId="1" text="KO">
+    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="KO">
       <formula>NOT(ISERROR(SEARCH("KO",G2)))</formula>
     </cfRule>
-    <cfRule type="containsText" priority="4" operator="containsText" dxfId="0" text="OK">
+    <cfRule type="containsText" dxfId="0" priority="4" operator="containsText" text="OK">
       <formula>NOT(ISERROR(SEARCH("OK",G2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId1"/>
+    <hyperlink ref="H2" r:id="rId1" xr:uid="{CEE99923-7872-4B7D-8DAD-4C911AA89078}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Web/TestCasesWeb/Modificadores.xlsx
+++ b/Web/TestCasesWeb/Modificadores.xlsx
@@ -97,7 +97,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -125,9 +125,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -540,17 +537,17 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>Modifiers page home is displayed correctly.</t>
-        </is>
-      </c>
-      <c r="G2" s="10" t="inlineStr">
-        <is>
-          <t>FIXED</t>
+          <t>1. Modifiers page home is not correctly.</t>
+        </is>
+      </c>
+      <c r="G2" s="7" t="inlineStr">
+        <is>
+          <t>KO</t>
         </is>
       </c>
       <c r="H2" s="8" t="inlineStr">
         <is>
-          <t>Fixed: added optional chaining (group.modifiers ?? []).flatMap(m =&gt; m.options ?? []) to prevent TypeError crash when modifier group has null/undefined modifiers.</t>
+          <t>https://drive.google.com/file/d/1G42M-IstesnZZMU-ySrYm7Y1F5BSn7oO/view?usp=drive_link</t>
         </is>
       </c>
     </row>

--- a/Web/TestCasesWeb/Modificadores.xlsx
+++ b/Web/TestCasesWeb/Modificadores.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\Web\TestCases\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\Web\TestCasesWeb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12FB2E63-6B42-4739-AF90-9417EAE1E8BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8626264-DD9E-490C-BF05-844730E7239D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="43">
   <si>
     <t>Num</t>
   </si>
@@ -66,9 +66,6 @@
   <si>
     <t xml:space="preserve">1. The user sees the modifiers page home.
 </t>
-  </si>
-  <si>
-    <t>1. Modifiers page home is not correctly.</t>
   </si>
   <si>
     <t>KO</t>
@@ -144,15 +141,6 @@
     <t>1. The modifier group is shown.</t>
   </si>
   <si>
-    <t>1. The modifier group is not created</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1JJLWdn5Tl9M0nQndOBVEbRRAHbzRwH13/view?usp=drive_link</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1G42M-IstesnZZMU-ySrYm7Y1F5BSn7oO/view?usp=drive_link</t>
-  </si>
-  <si>
     <t>Modify status modifier group</t>
   </si>
   <si>
@@ -168,6 +156,15 @@
   </si>
   <si>
     <t>MODIF008</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1JJLWdn5Tl9M0nQndOBVEbRRAHbzRwH13/view?usp=drive_link
+15/04/26: SOLUCIONADO: ModifiersPage.tsx - el handleSubmit del padre ahora hace 'throw e' después de console.error(e). Esto permite que el ModifierGroupModal reciba el error y muestre el mensaje submitError al usuario en lugar de cerrar silenciosamente.</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1G42M-IstesnZZMU-ySrYm7Y1F5BSn7oO/view?usp=drive_link
+15/04/26: Fixed: added optional chaining (group.modifiers ?? []).flatMap(m =&gt; m.options ?? []) to prevent TypeError crash when modifier group has null/undefined modifiers.
+17/04/26: BLOQUEANTE: La descripción de una opción muy larga, hace desaparecer la funcionalidad: MOD003.jpg</t>
   </si>
 </sst>
 </file>
@@ -262,14 +259,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -647,7 +644,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" s="5" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" s="5" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -663,14 +660,12 @@
       <c r="E2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="3"/>
+      <c r="G2" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="7" t="s">
-        <v>16</v>
-      </c>
       <c r="H2" s="8" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="5" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -681,22 +676,20 @@
         <v>9</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>37</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="F3" s="3"/>
       <c r="G3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>38</v>
+        <v>22</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:8" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -707,19 +700,19 @@
         <v>10</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>33</v>
-      </c>
       <c r="F4" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H4" s="4"/>
     </row>
@@ -731,19 +724,19 @@
         <v>11</v>
       </c>
       <c r="C5" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="E5" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="F5" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H5" s="4"/>
     </row>
@@ -752,22 +745,22 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H6" s="4"/>
     </row>
@@ -776,22 +769,22 @@
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="D7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G7" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>23</v>
       </c>
       <c r="H7" s="4"/>
     </row>
@@ -800,22 +793,22 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D8" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>36</v>
-      </c>
       <c r="F8" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H8" s="4"/>
     </row>
@@ -824,22 +817,22 @@
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H9" s="4"/>
     </row>
@@ -862,7 +855,8 @@
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="H2" r:id="rId1" xr:uid="{CEE99923-7872-4B7D-8DAD-4C911AA89078}"/>
+    <hyperlink ref="H3" r:id="rId1" display="https://drive.google.com/file/d/1JJLWdn5Tl9M0nQndOBVEbRRAHbzRwH13/view?usp=drive_link_x000a_15/04/26: SOLUCIONADO: ModifiersPage.tsx - el handleSubmit del padre ahora hace 'throw e' después de console.error(e). Esto permite que el ModifierGroupModal reciba el error y muestre el mensaje submitError al usuario en lugar de cerrar silenciosamente." xr:uid="{A2557506-81EA-4FF7-84E5-93B963A125B6}"/>
+    <hyperlink ref="H2" r:id="rId2" display="https://drive.google.com/file/d/1G42M-IstesnZZMU-ySrYm7Y1F5BSn7oO/view?usp=drive_link_x000a_15/04/26: Fixed: added optional chaining (group.modifiers ?? []).flatMap(m =&gt; m.options ?? []) to prevent TypeError crash when modifier group has null/undefined modifiers._x000a_17/04/26: BLOQUEANTE: La descripción de una opción muy larga, hace desaparecer la funcionalidad: MOD003.jpg" xr:uid="{59579ADC-DDBE-4B78-BA43-F9F09A1A16DC}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Web/TestCasesWeb/Modificadores.xlsx
+++ b/Web/TestCasesWeb/Modificadores.xlsx
@@ -262,7 +262,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1">

--- a/Web/TestCasesWeb/Modificadores.xlsx
+++ b/Web/TestCasesWeb/Modificadores.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\Web\TestCasesWeb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8626264-DD9E-490C-BF05-844730E7239D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3347472-B6FA-4EB3-962F-642A6DEE76CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="50">
   <si>
     <t>Num</t>
   </si>
@@ -58,41 +58,16 @@
     <t>MODIF004</t>
   </si>
   <si>
-    <t>Modifiers page home</t>
-  </si>
-  <si>
-    <t>1. Modifiers page home is correctly.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. The user sees the modifiers page home.
-</t>
-  </si>
-  <si>
     <t>KO</t>
   </si>
   <si>
-    <t>Create modifier group</t>
-  </si>
-  <si>
-    <t>Find modifier group</t>
-  </si>
-  <si>
-    <t>Modify modifier group</t>
-  </si>
-  <si>
     <t>MODIF005</t>
   </si>
   <si>
     <t>MODIF006</t>
   </si>
   <si>
-    <t>Create modifier group without mandatory parameters</t>
-  </si>
-  <si>
     <t>OK</t>
-  </si>
-  <si>
-    <t>Cancel create modifier group</t>
   </si>
   <si>
     <t xml:space="preserve">1. The user clicks "Crear primer grupo"
@@ -101,19 +76,10 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">1. The user clicks "Crear primer grupo"
-2. Fill mandatory fields
-3. The user clicks "Cancelar"
-</t>
-  </si>
-  <si>
     <t>1. An error is shown</t>
   </si>
   <si>
     <t>1. The creation is cancelled.</t>
-  </si>
-  <si>
-    <t>Delete modifier group</t>
   </si>
   <si>
     <t xml:space="preserve">1. The user selects a modifier group
@@ -135,13 +101,7 @@
     <t>1. The modifier group is created</t>
   </si>
   <si>
-    <t>1. The user search a modifier group</t>
-  </si>
-  <si>
     <t>1. The modifier group is shown.</t>
-  </si>
-  <si>
-    <t>Modify status modifier group</t>
   </si>
   <si>
     <t xml:space="preserve">1. The user selects a modifier group
@@ -149,9 +109,6 @@
 </t>
   </si>
   <si>
-    <t>1. The status of modifier group is updated.</t>
-  </si>
-  <si>
     <t>MODIF007</t>
   </si>
   <si>
@@ -165,6 +122,75 @@
     <t>https://drive.google.com/file/d/1G42M-IstesnZZMU-ySrYm7Y1F5BSn7oO/view?usp=drive_link
 15/04/26: Fixed: added optional chaining (group.modifiers ?? []).flatMap(m =&gt; m.options ?? []) to prevent TypeError crash when modifier group has null/undefined modifiers.
 17/04/26: BLOQUEANTE: La descripción de una opción muy larga, hace desaparecer la funcionalidad: MOD003.jpg</t>
+  </si>
+  <si>
+    <t>Modifiers page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. The user sees the modifiers page.
+</t>
+  </si>
+  <si>
+    <t>1. Modifiers page is correctly.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modifiers: Modify </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modifiers: Delete </t>
+  </si>
+  <si>
+    <t>Modifiers: Create, cancel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. The user clicks "Crear primer grupo"
+2. No fill mandatory fields
+3. The user clicks "Crear"
+</t>
+  </si>
+  <si>
+    <t>Modifiers: Create without mandatory parameters</t>
+  </si>
+  <si>
+    <t>Modifiers:  search</t>
+  </si>
+  <si>
+    <t>1. The user searchs a modifier group</t>
+  </si>
+  <si>
+    <t>Modifiers: deactivate</t>
+  </si>
+  <si>
+    <t>Modifiers: activate</t>
+  </si>
+  <si>
+    <t>Se han desactivado todos los modificadores, y luego se ha activado solo uno, pero en el POS no aparece: MOD006_1.jpg y MOD006_2.jpg</t>
+  </si>
+  <si>
+    <t>1. The status of modifier group is deactivated.</t>
+  </si>
+  <si>
+    <t>1. The status of modifier group is activated.</t>
+  </si>
+  <si>
+    <t>MODIF009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. The user clicks "Crear primer grupo"
+2. The user clicks "Cancelar"
+</t>
+  </si>
+  <si>
+    <t>Modifiers: Create, mandatory fields</t>
+  </si>
+  <si>
+    <t>Modifiers: Create, all fields</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. The user clicks "Crear primer grupo"
+2. Fill all fields
+3. The user clicks "Crear"
+</t>
   </si>
 </sst>
 </file>
@@ -608,7 +634,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="15" customWidth="1"/>
@@ -652,20 +678,20 @@
         <v>8</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="F2" s="3"/>
       <c r="G2" s="6" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="5" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -676,165 +702,217 @@
         <v>9</v>
       </c>
       <c r="C3" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>24</v>
-      </c>
       <c r="E3" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F3" s="3"/>
+        <v>23</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="G3" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" s="5" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H4" s="4"/>
+        <v>15</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="5" spans="1:8" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
+        <v>3</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" s="4"/>
+    </row>
+    <row r="6" spans="1:8" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A6" s="4">
         <v>4</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B6" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G5" s="1" t="s">
+      <c r="C6" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="H5" s="4"/>
-    </row>
-    <row r="6" spans="1:8" s="5" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A6" s="4">
+      <c r="F6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6" s="4"/>
+    </row>
+    <row r="7" spans="1:8" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A7" s="4">
         <v>5</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B7" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" s="3" t="s">
+      <c r="E7" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7" s="4"/>
+    </row>
+    <row r="8" spans="1:8" s="5" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A8" s="4">
+        <v>6</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H8" s="4"/>
+    </row>
+    <row r="9" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="4">
+        <v>7</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H9" s="4"/>
+    </row>
+    <row r="10" spans="1:8" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A10" s="4">
+        <v>8</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D10" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H6" s="4"/>
-    </row>
-    <row r="7" spans="1:8" s="5" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A7" s="4">
-        <v>6</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H7" s="4"/>
-    </row>
-    <row r="8" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="4">
-        <v>7</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H8" s="4"/>
-    </row>
-    <row r="9" spans="1:8" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A9" s="4">
-        <v>8</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H9" s="4"/>
+      <c r="E10" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H10" s="4"/>
+    </row>
+    <row r="11" spans="1:8" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A11" s="4">
+        <v>9</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F11" s="3"/>
+      <c r="G11" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>42</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
@@ -846,7 +924,7 @@
       <formula>NOT(ISERROR(SEARCH("BL",G2)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G9">
+  <conditionalFormatting sqref="G2:G11">
     <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="KO">
       <formula>NOT(ISERROR(SEARCH("KO",G2)))</formula>
     </cfRule>
@@ -857,6 +935,7 @@
   <hyperlinks>
     <hyperlink ref="H3" r:id="rId1" display="https://drive.google.com/file/d/1JJLWdn5Tl9M0nQndOBVEbRRAHbzRwH13/view?usp=drive_link_x000a_15/04/26: SOLUCIONADO: ModifiersPage.tsx - el handleSubmit del padre ahora hace 'throw e' después de console.error(e). Esto permite que el ModifierGroupModal reciba el error y muestre el mensaje submitError al usuario en lugar de cerrar silenciosamente." xr:uid="{A2557506-81EA-4FF7-84E5-93B963A125B6}"/>
     <hyperlink ref="H2" r:id="rId2" display="https://drive.google.com/file/d/1G42M-IstesnZZMU-ySrYm7Y1F5BSn7oO/view?usp=drive_link_x000a_15/04/26: Fixed: added optional chaining (group.modifiers ?? []).flatMap(m =&gt; m.options ?? []) to prevent TypeError crash when modifier group has null/undefined modifiers._x000a_17/04/26: BLOQUEANTE: La descripción de una opción muy larga, hace desaparecer la funcionalidad: MOD003.jpg" xr:uid="{59579ADC-DDBE-4B78-BA43-F9F09A1A16DC}"/>
+    <hyperlink ref="H4" r:id="rId3" display="https://drive.google.com/file/d/1JJLWdn5Tl9M0nQndOBVEbRRAHbzRwH13/view?usp=drive_link_x000a_15/04/26: SOLUCIONADO: ModifiersPage.tsx - el handleSubmit del padre ahora hace 'throw e' después de console.error(e). Esto permite que el ModifierGroupModal reciba el error y muestre el mensaje submitError al usuario en lugar de cerrar silenciosamente." xr:uid="{E52C7B05-252F-4B38-B7FD-F2CFD68A6C33}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Web/TestCasesWeb/Modificadores.xlsx
+++ b/Web/TestCasesWeb/Modificadores.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\Web\TestCasesWeb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3347472-B6FA-4EB3-962F-642A6DEE76CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C60A9006-CBBE-410E-BAE1-E29784E0B80C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="51">
   <si>
     <t>Num</t>
   </si>
@@ -191,6 +191,9 @@
 2. Fill all fields
 3. The user clicks "Crear"
 </t>
+  </si>
+  <si>
+    <t>MODIF010</t>
   </si>
 </sst>
 </file>
@@ -722,10 +725,10 @@
     </row>
     <row r="4" spans="1:8" s="5" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>48</v>
@@ -748,10 +751,10 @@
     </row>
     <row r="5" spans="1:8" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>35</v>
@@ -772,10 +775,10 @@
     </row>
     <row r="6" spans="1:8" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>33</v>
@@ -796,10 +799,10 @@
     </row>
     <row r="7" spans="1:8" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>34</v>
@@ -820,10 +823,10 @@
     </row>
     <row r="8" spans="1:8" s="5" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>37</v>
@@ -844,10 +847,10 @@
     </row>
     <row r="9" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>38</v>
@@ -868,10 +871,10 @@
     </row>
     <row r="10" spans="1:8" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>40</v>
@@ -892,10 +895,10 @@
     </row>
     <row r="11" spans="1:8" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>41</v>

--- a/Web/TestCasesWeb/Modificadores.xlsx
+++ b/Web/TestCasesWeb/Modificadores.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\Web\TestCasesWeb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C60A9006-CBBE-410E-BAE1-E29784E0B80C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF219B52-A776-4288-8B29-56974281C084}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="52">
   <si>
     <t>Num</t>
   </si>
@@ -104,11 +104,6 @@
     <t>1. The modifier group is shown.</t>
   </si>
   <si>
-    <t xml:space="preserve">1. The user selects a modifier group
-2. Change status
-</t>
-  </si>
-  <si>
     <t>MODIF007</t>
   </si>
   <si>
@@ -194,6 +189,16 @@
   </si>
   <si>
     <t>MODIF010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. The user selects a modifier group
+2. Desactivate modifier group
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. The user selects a modifier group
+2. Activate modifier group
+</t>
   </si>
 </sst>
 </file>
@@ -681,20 +686,20 @@
         <v>8</v>
       </c>
       <c r="C2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>31</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>32</v>
       </c>
       <c r="F2" s="3"/>
       <c r="G2" s="6" t="s">
         <v>12</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="5" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -705,7 +710,7 @@
         <v>9</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>16</v>
@@ -720,7 +725,7 @@
         <v>15</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:8" s="5" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -731,10 +736,10 @@
         <v>10</v>
       </c>
       <c r="C4" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>23</v>
@@ -746,7 +751,7 @@
         <v>15</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:8" s="5" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -757,10 +762,10 @@
         <v>11</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>18</v>
@@ -781,7 +786,7 @@
         <v>13</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>21</v>
@@ -805,7 +810,7 @@
         <v>14</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>19</v>
@@ -826,13 +831,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>17</v>
@@ -850,13 +855,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C9" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>38</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>39</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>24</v>
@@ -874,19 +879,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>15</v>
@@ -898,23 +903,23 @@
         <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F11" s="3"/>
       <c r="G11" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
